--- a/data/raw/GLNPO 2024 Spring/Superior/D20/Zoops/SU 05 D20 Spring 2024 24GS00I94 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Superior/D20/Zoops/SU 05 D20 Spring 2024 24GS00I94 Zoop.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccm243\Desktop\GLNPO Counts\2024\Spring\Superior\Zoop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Superior\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67ED4C65-91DB-4E85-AFD2-0C5762215EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECC9A84-1792-46AC-8A83-5F268813A19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D68872C4-2689-46C2-B172-A72ECBA05D09}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D68872C4-2689-46C2-B172-A72ECBA05D09}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$102</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1475" r:id="rId2"/>
+    <pivotCache cacheId="30" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -419,7 +419,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -437,16 +437,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2578,7 +2577,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B3BACEE-A3B9-449F-8247-C1D724746FEC}" name="PivotTable2" cacheId="1475" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B3BACEE-A3B9-449F-8247-C1D724746FEC}" name="PivotTable2" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T4:X13" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -2997,19 +2996,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D999DF-1CB0-4241-B43B-C10652CEEC0C}">
   <dimension ref="A1:X102"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.140625" customWidth="1"/>
-    <col min="23" max="23" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.109375" customWidth="1"/>
+    <col min="23" max="23" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3065,7 +3064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3118,7 +3117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3171,7 +3170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3230,7 +3229,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -3298,7 +3297,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -3353,18 +3352,17 @@
       <c r="T6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="U6" s="11">
-        <v>18</v>
-      </c>
-      <c r="V6" s="11">
+      <c r="U6">
+        <v>18</v>
+      </c>
+      <c r="V6">
         <v>40</v>
       </c>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11">
+      <c r="X6">
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -3419,16 +3417,14 @@
       <c r="T7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="U7" s="11">
+      <c r="U7">
         <v>37</v>
       </c>
-      <c r="V7" s="11"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11">
+      <c r="X7">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -3483,18 +3479,17 @@
       <c r="T8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="U8" s="11">
+      <c r="U8">
         <v>2</v>
       </c>
-      <c r="V8" s="11">
+      <c r="V8">
         <v>5</v>
       </c>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11">
+      <c r="X8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -3549,18 +3544,17 @@
       <c r="T9" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="U9" s="11">
+      <c r="U9">
         <v>0</v>
       </c>
-      <c r="V9" s="11">
-        <v>1</v>
-      </c>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3615,16 +3609,14 @@
       <c r="T10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="U10" s="11">
+      <c r="U10">
         <v>101</v>
       </c>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11">
+      <c r="X10">
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -3679,16 +3671,14 @@
       <c r="T11" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="U11" s="11">
+      <c r="U11">
         <v>30</v>
       </c>
-      <c r="V11" s="11"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11">
+      <c r="X11">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -3743,20 +3733,20 @@
       <c r="T12" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="U12" s="11">
-        <v>1</v>
-      </c>
-      <c r="V12" s="11">
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
         <v>0</v>
       </c>
-      <c r="W12" s="11">
+      <c r="W12">
         <v>4</v>
       </c>
-      <c r="X12" s="11">
+      <c r="X12">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -3811,20 +3801,20 @@
       <c r="T13" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="U13" s="11">
+      <c r="U13">
         <v>189</v>
       </c>
-      <c r="V13" s="11">
+      <c r="V13">
         <v>46</v>
       </c>
-      <c r="W13" s="11">
+      <c r="W13">
         <v>4</v>
       </c>
-      <c r="X13" s="11">
+      <c r="X13">
         <v>239</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -3877,7 +3867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -3930,7 +3920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -3982,17 +3972,17 @@
       <c r="Q16">
         <v>1</v>
       </c>
-      <c r="T16" s="12" t="s">
+      <c r="T16" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="U16" s="13" t="s">
+      <c r="U16" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="V16" s="14">
+      <c r="V16" s="12">
         <v>0.998</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -4045,14 +4035,14 @@
         <v>1</v>
       </c>
       <c r="T17" s="15"/>
-      <c r="U17" s="13" t="s">
+      <c r="U17" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="V17" s="14">
+      <c r="V17" s="12">
         <v>0.999</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -4104,17 +4094,17 @@
       <c r="Q18">
         <v>1</v>
       </c>
-      <c r="T18" s="12" t="s">
+      <c r="T18" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="U18" s="13" t="s">
+      <c r="U18" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="V18" s="14">
+      <c r="V18" s="12">
         <v>0.996</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -4167,14 +4157,14 @@
         <v>1</v>
       </c>
       <c r="T19" s="15"/>
-      <c r="U19" s="13" t="s">
+      <c r="U19" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="V19" s="14">
+      <c r="V19" s="12">
         <v>0.996</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -4226,15 +4216,15 @@
       <c r="Q20">
         <v>1</v>
       </c>
-      <c r="T20" s="16" t="s">
+      <c r="T20" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="U20" s="17" t="s">
+      <c r="U20" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="V20" s="18"/>
-    </row>
-    <row r="21" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V20" s="17"/>
+    </row>
+    <row r="21" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -4286,15 +4276,15 @@
       <c r="Q21">
         <v>1</v>
       </c>
-      <c r="T21" s="16" t="s">
+      <c r="T21" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="U21" s="17" t="s">
+      <c r="U21" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="V21" s="18"/>
-    </row>
-    <row r="22" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V21" s="17"/>
+    </row>
+    <row r="22" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -4346,13 +4336,13 @@
       <c r="Q22">
         <v>1</v>
       </c>
-      <c r="T22" s="13" t="s">
+      <c r="T22" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="U22" s="17"/>
-      <c r="V22" s="18"/>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U22" s="16"/>
+      <c r="V22" s="17"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -4405,7 +4395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -4458,7 +4448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -4511,7 +4501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -4564,7 +4554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -4617,7 +4607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -4670,7 +4660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -4723,7 +4713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -4776,7 +4766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -4829,7 +4819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -4882,7 +4872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -4935,7 +4925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -4988,7 +4978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -5041,7 +5031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -5094,7 +5084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -5147,7 +5137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -5200,7 +5190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -5253,7 +5243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -5306,7 +5296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -5359,7 +5349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -5412,7 +5402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -5465,7 +5455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -5518,7 +5508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -5571,7 +5561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -5624,7 +5614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -5677,7 +5667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -5730,7 +5720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -5783,7 +5773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -5836,7 +5826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -5889,7 +5879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -5942,7 +5932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -5995,7 +5985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -6048,7 +6038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -6101,7 +6091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -6154,7 +6144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -6207,7 +6197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -6260,7 +6250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -6313,7 +6303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -6366,7 +6356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -6419,7 +6409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -6472,7 +6462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -6525,7 +6515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -6578,7 +6568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -6631,7 +6621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -6684,7 +6674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -6737,7 +6727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -6790,7 +6780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -6843,7 +6833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -6896,7 +6886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -6949,7 +6939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -7002,7 +6992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -7055,7 +7045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -7108,7 +7098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -7161,7 +7151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -7214,7 +7204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -7267,7 +7257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -7320,7 +7310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -7373,7 +7363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -7426,7 +7416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -7479,7 +7469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -7532,7 +7522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -7585,7 +7575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -7638,7 +7628,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -7691,7 +7681,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -7744,7 +7734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -7797,7 +7787,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -7850,7 +7840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -7903,7 +7893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -7956,7 +7946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -8009,7 +7999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -8062,7 +8052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -8103,7 +8093,7 @@
         <v>49</v>
       </c>
       <c r="N93" s="4" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O93">
         <v>0.51700000000000002</v>
@@ -8118,7 +8108,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -8171,7 +8161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -8224,7 +8214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -8277,7 +8267,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -8330,7 +8320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -8383,7 +8373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -8436,7 +8426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -8489,7 +8479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>18</v>
       </c>
@@ -8530,7 +8520,7 @@
         <v>49</v>
       </c>
       <c r="N101" s="8" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="O101" s="5" t="s">
         <v>29</v>
@@ -8542,7 +8532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>18</v>
       </c>
